--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487976_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487976_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2556</v>
+        <v>7.6807</v>
       </c>
       <c r="E2" t="n">
-        <v>8.028499999999999</v>
+        <v>8.537800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7729</v>
+        <v>-0.8572</v>
       </c>
       <c r="G2" t="n">
         <v>6.5713</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2654</v>
+        <v>0.1597</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2899</v>
+        <v>0.2194</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0245</v>
+        <v>-0.0597</v>
       </c>
       <c r="V2" t="n">
         <v>0.5532</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1606</v>
+        <v>6.4205</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8579</v>
+        <v>6.0616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3027</v>
+        <v>0.3589</v>
       </c>
       <c r="G3" t="n">
         <v>7.6614</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5587</v>
+        <v>0.8186</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0552</v>
+        <v>0.2589</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.5597</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8701</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8646</v>
+        <v>6.135</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2174</v>
+        <v>7.0947</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3528</v>
+        <v>-0.9597</v>
       </c>
       <c r="G4" t="n">
         <v>4.3413</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4353</v>
+        <v>0.8351</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4771</v>
+        <v>0.4002</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0418</v>
+        <v>0.4349</v>
       </c>
       <c r="V4" t="n">
         <v>1.1568</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5164</v>
+        <v>4.873</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8386</v>
+        <v>1.1672</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6778</v>
+        <v>3.7059</v>
       </c>
       <c r="G5" t="n">
         <v>2.5652</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.4377</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3596</v>
+        <v>-0.031</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4407</v>
+        <v>0.4688</v>
       </c>
       <c r="V5" t="n">
         <v>1.4737</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0501</v>
+        <v>4.1584</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9156</v>
+        <v>2.8554</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1345</v>
+        <v>1.303</v>
       </c>
       <c r="G6" t="n">
         <v>2.8653</v>
@@ -922,13 +922,13 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6695</v>
+        <v>0.4387</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9873</v>
+        <v>-0.0476</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3178</v>
+        <v>0.4863</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5331</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5348</v>
+        <v>1.6068</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1066</v>
+        <v>1.1123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4282</v>
+        <v>0.4945</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1756</v>
+        <v>-0.495</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7584</v>
+        <v>-0.1295</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5828</v>
+        <v>-0.3655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4572</v>
+        <v>0.423</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2386</v>
+        <v>0.2623</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6958</v>
+        <v>0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6328</v>
+        <v>-0.918</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5198</v>
+        <v>-0.3918</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.113</v>
+        <v>-0.5262</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5769</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1086</v>
+        <v>0.9104</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2967</v>
+        <v>0.6893</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1881</v>
+        <v>0.2211</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7947</v>
+        <v>-0.1962</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3278</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9405</v>
+        <v>0.8468</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4179</v>
+        <v>0.194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5226</v>
+        <v>0.6529</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.495</v>
+        <v>-0.1756</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1295</v>
+        <v>-2.7584</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3655</v>
+        <v>2.5828</v>
       </c>
       <c r="J8" t="n">
-        <v>0.423</v>
+        <v>0.4572</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2623</v>
+        <v>-2.2386</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1607</v>
+        <v>2.6958</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.918</v>
+        <v>-0.6328</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3918</v>
+        <v>-0.5198</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5262</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S8" t="n">
-        <v>1.244</v>
+        <v>1.4207</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9949</v>
+        <v>1.3841</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2491</v>
+        <v>0.0365</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1962</v>
+        <v>-0.7947</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1962</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>I. MARTIN ARROYO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3767</v>
+        <v>-0.1157</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1714</v>
+        <v>-0.7415</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5481</v>
+        <v>0.6259</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0939</v>
+        <v>-0.2717</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7175</v>
+        <v>-0.2717</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6237</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9167</v>
+        <v>-0.6791</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.997</v>
+        <v>-0.6791</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8228</v>
+        <v>0.4075</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2795</v>
+        <v>0.4075</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5433</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8759</v>
+        <v>0.156</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9435</v>
+        <v>-0.0624</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.2184</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MARTIN ARROYO</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0595</v>
+        <v>-0.1826</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7415</v>
+        <v>-1.6183</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.4357</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2717</v>
+        <v>-1.0939</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2717</v>
+        <v>-1.7175</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.6237</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6791</v>
+        <v>-1.9167</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6791</v>
+        <v>-1.997</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0804</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4075</v>
+        <v>0.8228</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4075</v>
+        <v>0.2795</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.5433</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2122</v>
+        <v>0.3166</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0624</v>
+        <v>0.4966</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2745</v>
+        <v>-0.18</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2994</v>
+        <v>-3.5739</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9302</v>
+        <v>-4.0923</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6307</v>
+        <v>0.5184</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4521</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6402</v>
+        <v>0.0853</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8515</v>
+        <v>-0.0136</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2113</v>
+        <v>0.0989</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4142</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5174</v>
+        <v>-5.6621</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7463</v>
+        <v>-4.3575</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7712</v>
+        <v>-1.3046</v>
       </c>
       <c r="G12" t="n">
         <v>-4.98</v>
@@ -1390,13 +1390,13 @@
         <v>1.3876</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2395</v>
+        <v>1.0948</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9435</v>
+        <v>0.3323</v>
       </c>
       <c r="U12" t="n">
-        <v>1.296</v>
+        <v>0.7625</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1911</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.9594</v>
+        <v>-6.5976</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8086</v>
+        <v>-3.503</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1508</v>
+        <v>-3.0946</v>
       </c>
       <c r="G13" t="n">
         <v>-6.2013</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6196</v>
+        <v>-0.2579</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3413</v>
+        <v>-0.0357</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2783</v>
+        <v>-0.2222</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3278</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.8636</v>
+        <v>15.5893</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9845</v>
+        <v>12.7104</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8789</v>
+        <v>2.879099999999999</v>
       </c>
       <c r="G14" t="n">
         <v>10.3349</v>
@@ -1546,10 +1546,10 @@
         <v>16.8492</v>
       </c>
       <c r="S14" t="n">
-        <v>5.69</v>
+        <v>6.4157</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8647</v>
+        <v>3.5905</v>
       </c>
       <c r="U14" t="n">
         <v>2.8252</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6149</v>
+        <v>3.7466</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4489</v>
+        <v>2.819</v>
       </c>
       <c r="F15" t="n">
-        <v>1.166</v>
+        <v>0.9277</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4836</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1668</v>
+        <v>1.2985</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0853</v>
+        <v>0.4554</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0815</v>
+        <v>0.8431</v>
       </c>
       <c r="V15" t="n">
         <v>1.5441</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.817</v>
+        <v>2.6483</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3531</v>
+        <v>4.9643</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5362</v>
+        <v>-2.3161</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3729</v>
@@ -1780,13 +1780,13 @@
         <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4048</v>
+        <v>-0.5736</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7488</v>
+        <v>-0.1376</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6561</v>
+        <v>-0.436</v>
       </c>
       <c r="V17" t="n">
         <v>1.8107</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5095</v>
+        <v>1.2376</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0196</v>
+        <v>2.2233</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.51</v>
+        <v>-0.9857</v>
       </c>
       <c r="G18" t="n">
         <v>0.5906</v>
@@ -1858,13 +1858,13 @@
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2705</v>
+        <v>-0.5424</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6864</v>
+        <v>-0.4826</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5841</v>
+        <v>-0.0597</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2633</v>
+        <v>0.4213</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0422</v>
+        <v>0.0596</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3055</v>
+        <v>0.3617</v>
       </c>
       <c r="G19" t="n">
         <v>0.0901</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.025</v>
+        <v>0.1331</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9835</v>
+        <v>-1.0027</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.908</v>
+        <v>-1.7043</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.7017</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9821</v>
@@ -2014,13 +2014,13 @@
         <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9131</v>
+        <v>-0.9323</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6826</v>
+        <v>-0.4788</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2306</v>
+        <v>-0.4535</v>
       </c>
       <c r="V20" t="n">
         <v>-0.674</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7572</v>
+        <v>-2.7653</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4516</v>
+        <v>-2.5534</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3057</v>
+        <v>-0.2118</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0252</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3384</v>
+        <v>0.3303</v>
       </c>
       <c r="T21" t="n">
-        <v>0.191</v>
+        <v>0.0891</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1474</v>
+        <v>0.2412</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8811</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6686</v>
+        <v>-4.0678</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0603</v>
+        <v>-2.7547</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6083</v>
+        <v>-1.3132</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1187</v>
@@ -2170,13 +2170,13 @@
         <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0257</v>
+        <v>-0.4249</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8698</v>
+        <v>-0.5642</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1559</v>
+        <v>0.1393</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5331</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1204</v>
+        <v>-4.1886</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0758</v>
+        <v>-4.6683</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0446</v>
+        <v>0.4797</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1157</v>
@@ -2248,13 +2248,13 @@
         <v>1.5858</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7272</v>
+        <v>0.2047</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.624</v>
+        <v>-0.2165</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1032</v>
+        <v>0.4212</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8811</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5006</v>
+        <v>-4.6752</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6127</v>
+        <v>-1.3071</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8879</v>
+        <v>-3.3681</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5788</v>
@@ -2326,13 +2326,13 @@
         <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2745</v>
+        <v>-1.4491</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2369</v>
+        <v>-0.9313</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0376</v>
+        <v>-0.5178</v>
       </c>
       <c r="V24" t="n">
         <v>1.7403</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0592</v>
+        <v>-6.4758</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5712</v>
+        <v>-2.9787</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.488</v>
+        <v>-3.4971</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3599</v>
@@ -2404,13 +2404,13 @@
         <v>1.784</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5543</v>
+        <v>-0.9709</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1906</v>
+        <v>-0.5981</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3637</v>
+        <v>-0.3728</v>
       </c>
       <c r="V25" t="n">
         <v>3.0178</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.8635</v>
+        <v>-12.1003</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.8789</v>
+        <v>-2.879000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.9846</v>
+        <v>-9.2212</v>
       </c>
       <c r="G26" t="n">
         <v>-10.3349</v>
@@ -2482,13 +2482,13 @@
         <v>14.8667</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.6899</v>
+        <v>-2.9266</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.8252</v>
+        <v>-2.8251</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8649</v>
+        <v>-0.1014000000000002</v>
       </c>
       <c r="V26" t="n">
         <v>3.1436</v>
